--- a/update-dependencies-fr-core-annuaire/ig/StructureDefinition-ror-internal-organization.xlsx
+++ b/update-dependencies-fr-core-annuaire/ig/StructureDefinition-ror-internal-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T08:09:55+00:00</t>
+    <t>2026-08-20T16:34:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/update-dependencies-fr-core-annuaire/ig/StructureDefinition-ror-internal-organization.xlsx
+++ b/update-dependencies-fr-core-annuaire/ig/StructureDefinition-ror-internal-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T16:34:37+00:00</t>
+    <t>2026-08-21T09:28:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/update-dependencies-fr-core-annuaire/ig/StructureDefinition-ror-internal-organization.xlsx
+++ b/update-dependencies-fr-core-annuaire/ig/StructureDefinition-ror-internal-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T09:28:33+00:00</t>
+    <t>2026-08-21T09:39:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/update-dependencies-fr-core-annuaire/ig/StructureDefinition-ror-internal-organization.xlsx
+++ b/update-dependencies-fr-core-annuaire/ig/StructureDefinition-ror-internal-organization.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$119</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3150" uniqueCount="599">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4425" uniqueCount="671">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T09:39:43+00:00</t>
+    <t>2026-08-21T14:30:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1404,6 +1404,13 @@
     <t>Human contact for the organization.</t>
   </si>
   <si>
+    <t xml:space="preserve">profile:$this}
+</t>
+  </si>
+  <si>
+    <t>Slicing pour isoler la boîte MSS, conforme au profil standard AsMailboxMSSProfile</t>
+  </si>
+  <si>
     <t xml:space="preserve">org-3
 </t>
   </si>
@@ -1412,28 +1419,47 @@
 org-3:The telecom of an organization can never be of use 'home' {where(use = 'home').empty()}</t>
   </si>
   <si>
+    <t>ORC-22?</t>
+  </si>
+  <si>
+    <t>.telecom</t>
+  </si>
+  <si>
+    <t>./ContactPoints</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss</t>
+  </si>
+  <si>
+    <t>mailbox-mss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ContactPoint {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-mailbox-mss}
+</t>
+  </si>
+  <si>
+    <t>A contact detail for the organization</t>
+  </si>
+  <si>
     <t>boiteLettreMSS</t>
   </si>
   <si>
-    <t>ORC-22?</t>
-  </si>
-  <si>
-    <t>.telecom</t>
-  </si>
-  <si>
-    <t>./ContactPoints</t>
+    <t>Organization.telecom:mailbox-mss.id</t>
   </si>
   <si>
     <t>Organization.telecom.id</t>
   </si>
   <si>
+    <t>Organization.telecom:mailbox-mss.extension</t>
+  </si>
+  <si>
     <t>Organization.telecom.extension</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>Organization.telecom.extension:emailType</t>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:emailType</t>
   </si>
   <si>
     <t>emailType</t>
@@ -1443,7 +1469,7 @@
 </t>
   </si>
   <si>
-    <t>Champs permettant de préciser le type d'email (MSSANTE | APICRYPT | OSM | AutreMessagerie) dont il est question dans le cas où le point de contact est un email.</t>
+    <t>Type of email | type de messagerie électronique</t>
   </si>
   <si>
     <t>Extension permettant d'indiquer le type d'adresse email d'un ContactPoint.
@@ -1451,7 +1477,188 @@
  This extension allows to specify the type of mail used to contact the person.</t>
   </si>
   <si>
-    <t>Organization.telecom.extension:ror-telecom-communication-channel</t>
+    <t>Organization.telecom:mailbox-mss.extension:emailType.id</t>
+  </si>
+  <si>
+    <t>Organization.telecom.extension.id</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:emailType.extension</t>
+  </si>
+  <si>
+    <t>Organization.telecom.extension.extension</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:emailType.url</t>
+  </si>
+  <si>
+    <t>Organization.telecom.extension.url</t>
+  </si>
+  <si>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point-email-type</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:emailType.value[x]</t>
+  </si>
+  <si>
+    <t>Organization.telecom.extension.value[x]</t>
+  </si>
+  <si>
+    <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
+  &lt;system value="https://mos.esante.gouv.fr/NOS/TRE_R256-TypeMessagerie/FHIR/TRE-R256-TypeMessagerie"/&gt;
+  &lt;code value="MSSANTE"/&gt;
+  &lt;display value="MSSANTE"/&gt;
+&lt;/valueCoding&gt;</t>
+  </si>
+  <si>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-email-type|2.2.0</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata</t>
+  </si>
+  <si>
+    <t>as-mailbox-mss-metadata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-mailbox-mss-metadata|1.2.0-snapshot-2}
+</t>
+  </si>
+  <si>
+    <t>L'attribut 'responsible' n'est pas disponible en accès libre.</t>
+  </si>
+  <si>
+    <t>Extension contenant les métadonnées de la mailbox mss.</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.id</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:type</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>typeBAL : Type de boîte aux lettres.
+Valeurs possibles : ORG | APP | PER | CAB</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:type.id</t>
+  </si>
+  <si>
+    <t>Organization.telecom.extension.extension.id</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:type.extension</t>
+  </si>
+  <si>
+    <t>Organization.telecom.extension.extension.extension</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:type.url</t>
+  </si>
+  <si>
+    <t>Organization.telecom.extension.extension.url</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:type.value[x]</t>
+  </si>
+  <si>
+    <t>Organization.telecom.extension.extension.value[x]</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J139-TypeBAL-RASS/FHIR/JDV-J139-TypeBAL-RASS|20231124120000</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:description</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:description.id</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:description.extension</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:description.url</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:description.value[x]</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:responsible</t>
+  </si>
+  <si>
+    <t>responsible</t>
+  </si>
+  <si>
+    <t>responsable : Texte libre donnant les coordonnées de la (ou des) personne(s) responsable(s) au niveau opérationnel de la boîte aux lettres. Non renseigné pour les types de boîte aux lettres "PER".</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:responsible.id</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:responsible.extension</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:responsible.url</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:responsible.value[x]</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:service</t>
+  </si>
+  <si>
+    <t>service</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:service.id</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:service.extension</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:service.url</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:service.value[x]</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:listeRouge</t>
+  </si>
+  <si>
+    <t>listeRouge</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:listeRouge.id</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:listeRouge.extension</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:listeRouge.url</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:listeRouge.value[x]</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.url</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-mailbox-mss-metadata</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.value[x]</t>
+  </si>
+  <si>
+    <t>base64Binary
+booleancanonicalcodedatedateTimedecimalidinstantintegermarkdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioReferenceSampledDataSignatureTimingContactDetailContributorDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextDosageMeta</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:ror-telecom-communication-channel</t>
   </si>
   <si>
     <t>ror-telecom-communication-channel</t>
@@ -1467,7 +1674,7 @@
     <t>Extension créée dans le cadre du ROR spécifiant le canal ou la manière dont s'établit la communication</t>
   </si>
   <si>
-    <t>Organization.telecom.extension:ror-telecom-usage</t>
+    <t>Organization.telecom:mailbox-mss.extension:ror-telecom-usage</t>
   </si>
   <si>
     <t>ror-telecom-usage</t>
@@ -1483,7 +1690,7 @@
     <t>Extension créée dans le cadre du ROR qui précise l'utilisation du canal de communication</t>
   </si>
   <si>
-    <t>Organization.telecom.extension:ror-telecom-confidentiality-level</t>
+    <t>Organization.telecom:mailbox-mss.extension:ror-telecom-confidentiality-level</t>
   </si>
   <si>
     <t>ror-telecom-confidentiality-level</t>
@@ -1499,6 +1706,9 @@
     <t>Extension créée dans le cadre du ROR qui permet de définir le niveau de restriction de l'accès aux attributs de la classe Télécommunication.</t>
   </si>
   <si>
+    <t>Organization.telecom:mailbox-mss.system</t>
+  </si>
+  <si>
     <t>Organization.telecom.system</t>
   </si>
   <si>
@@ -1506,6 +1716,9 @@
   </si>
   <si>
     <t>Telecommunications form for contact point - what communications system is required to make use of the contact.</t>
+  </si>
+  <si>
+    <t>email</t>
   </si>
   <si>
     <t>Telecommunications form for contact point.</t>
@@ -1530,6 +1743,9 @@
     <t>./ContactPointType</t>
   </si>
   <si>
+    <t>Organization.telecom:mailbox-mss.value</t>
+  </si>
+  <si>
     <t>Organization.telecom.value</t>
   </si>
   <si>
@@ -1557,6 +1773,9 @@
     <t>./url</t>
   </si>
   <si>
+    <t>Organization.telecom:mailbox-mss.use</t>
+  </si>
+  <si>
     <t>Organization.telecom.use</t>
   </si>
   <si>
@@ -1588,6 +1807,9 @@
   </si>
   <si>
     <t>./ContactPointPurpose</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.rank</t>
   </si>
   <si>
     <t>Organization.telecom.rank</t>
@@ -1607,6 +1829,9 @@
   </si>
   <si>
     <t>ContactPoint.rank</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.period</t>
   </si>
   <si>
     <t>Organization.telecom.period</t>
@@ -2208,11 +2433,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO84"/>
+  <dimension ref="A1:AO119"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="55.20703125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="34.30078125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="83.53515625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="42.3828125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="35.05078125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -2221,7 +2446,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="136.7265625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2239,7 +2464,7 @@
     <col min="26" max="26" width="92.96875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="20.2734375" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="64.12890625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="64.90625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
@@ -8702,7 +8927,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
         <v>437</v>
       </c>
@@ -8779,16 +9004,16 @@
         <v>77</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>77</v>
+        <v>443</v>
       </c>
       <c r="AC56" t="s" s="2">
-        <v>77</v>
+        <v>444</v>
       </c>
       <c r="AD56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="AF56" t="s" s="2">
         <v>437</v>
@@ -8800,35 +9025,37 @@
         <v>79</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>445</v>
+        <v>77</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="57" hidden="true">
+    <row r="57">
       <c r="A57" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="C57" s="2"/>
+        <v>437</v>
+      </c>
+      <c r="C57" t="s" s="2">
+        <v>451</v>
+      </c>
       <c r="D57" t="s" s="2">
         <v>77</v>
       </c>
@@ -8837,10 +9064,10 @@
         <v>78</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>77</v>
@@ -8849,16 +9076,20 @@
         <v>77</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>104</v>
+        <v>452</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>105</v>
+        <v>453</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
+        <v>440</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>442</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>77</v>
       </c>
@@ -8906,31 +9137,31 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>107</v>
+        <v>437</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>77</v>
+        <v>445</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>77</v>
+        <v>446</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>77</v>
+        <v>454</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>77</v>
+        <v>447</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>108</v>
+        <v>448</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>77</v>
+        <v>449</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>77</v>
@@ -8938,10 +9169,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8949,10 +9180,10 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>451</v>
+        <v>78</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>77</v>
@@ -8964,13 +9195,13 @@
         <v>77</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>203</v>
+        <v>105</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>204</v>
+        <v>106</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -9009,31 +9240,31 @@
         <v>77</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>77</v>
@@ -9042,7 +9273,7 @@
         <v>77</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>77</v>
@@ -9053,23 +9284,21 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="C59" t="s" s="2">
-        <v>453</v>
-      </c>
+        <v>458</v>
+      </c>
+      <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>78</v>
+        <v>459</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>77</v>
@@ -9081,13 +9310,13 @@
         <v>77</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>454</v>
+        <v>111</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>455</v>
+        <v>203</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>456</v>
+        <v>204</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9126,16 +9355,16 @@
         <v>77</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AC59" t="s" s="2">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="AD59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="AF59" t="s" s="2">
         <v>118</v>
@@ -9168,15 +9397,15 @@
         <v>77</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="D60" t="s" s="2">
         <v>77</v>
@@ -9189,7 +9418,7 @@
         <v>88</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>77</v>
@@ -9198,13 +9427,13 @@
         <v>77</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9285,16 +9514,14 @@
         <v>77</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="C61" t="s" s="2">
-        <v>463</v>
-      </c>
+        <v>466</v>
+      </c>
+      <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
         <v>77</v>
       </c>
@@ -9306,7 +9533,7 @@
         <v>88</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>77</v>
@@ -9315,13 +9542,13 @@
         <v>77</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>464</v>
+        <v>104</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>465</v>
+        <v>105</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>466</v>
+        <v>106</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9372,19 +9599,19 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>77</v>
@@ -9393,7 +9620,7 @@
         <v>77</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>77</v>
@@ -9402,28 +9629,26 @@
         <v>77</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
         <v>467</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="C62" t="s" s="2">
         <v>468</v>
       </c>
+      <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>77</v>
@@ -9432,13 +9657,13 @@
         <v>77</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>469</v>
+        <v>111</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>470</v>
+        <v>203</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>471</v>
+        <v>204</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9477,16 +9702,16 @@
         <v>77</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AC62" t="s" s="2">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="AD62" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="AF62" t="s" s="2">
         <v>118</v>
@@ -9521,10 +9746,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9544,25 +9769,27 @@
         <v>77</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>178</v>
+        <v>133</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>473</v>
+        <v>255</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="N63" s="2"/>
+        <v>256</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>257</v>
+      </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q63" s="2"/>
       <c r="R63" t="s" s="2">
-        <v>77</v>
+        <v>471</v>
       </c>
       <c r="S63" t="s" s="2">
         <v>77</v>
@@ -9580,13 +9807,13 @@
         <v>77</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>169</v>
+        <v>77</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>475</v>
+        <v>77</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>476</v>
+        <v>77</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>77</v>
@@ -9604,42 +9831,42 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>477</v>
+        <v>259</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH63" t="s" s="2">
         <v>88</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>478</v>
+        <v>77</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>479</v>
+        <v>77</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>480</v>
+        <v>201</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>481</v>
+        <v>77</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>482</v>
+        <v>472</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>482</v>
+        <v>473</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9647,35 +9874,31 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G64" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>104</v>
+        <v>150</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>483</v>
+        <v>263</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>486</v>
-      </c>
+        <v>264</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>77</v>
       </c>
@@ -9684,7 +9907,7 @@
         <v>77</v>
       </c>
       <c r="S64" t="s" s="2">
-        <v>77</v>
+        <v>474</v>
       </c>
       <c r="T64" t="s" s="2">
         <v>77</v>
@@ -9699,13 +9922,11 @@
         <v>77</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y64" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="Y64" s="2"/>
       <c r="Z64" t="s" s="2">
-        <v>77</v>
+        <v>475</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>77</v>
@@ -9723,7 +9944,7 @@
         <v>77</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>487</v>
+        <v>265</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9738,16 +9959,16 @@
         <v>101</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>488</v>
+        <v>77</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>489</v>
+        <v>77</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>490</v>
+        <v>201</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>374</v>
+        <v>77</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>77</v>
@@ -9755,12 +9976,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>491</v>
+        <v>476</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="C65" s="2"/>
+        <v>458</v>
+      </c>
+      <c r="C65" t="s" s="2">
+        <v>477</v>
+      </c>
       <c r="D65" t="s" s="2">
         <v>77</v>
       </c>
@@ -9775,26 +9998,22 @@
         <v>77</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>178</v>
+        <v>478</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>492</v>
+        <v>479</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>495</v>
-      </c>
+        <v>480</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>77</v>
       </c>
@@ -9818,13 +10037,13 @@
         <v>77</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>169</v>
+        <v>77</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>496</v>
+        <v>77</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>497</v>
+        <v>77</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>77</v>
@@ -9842,31 +10061,31 @@
         <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>498</v>
+        <v>118</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>499</v>
+        <v>77</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>500</v>
+        <v>77</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>501</v>
+        <v>77</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>77</v>
@@ -9874,10 +10093,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>502</v>
+        <v>481</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>502</v>
+        <v>466</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9897,20 +10116,18 @@
         <v>77</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>503</v>
+        <v>104</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>504</v>
+        <v>105</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>506</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N66" s="2"/>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>77</v>
@@ -9959,7 +10176,7 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>507</v>
+        <v>107</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9971,13 +10188,13 @@
         <v>77</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>108</v>
@@ -9991,21 +10208,21 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>508</v>
+        <v>482</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>508</v>
+        <v>468</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>77</v>
@@ -10014,18 +10231,20 @@
         <v>77</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>262</v>
+        <v>111</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>509</v>
+        <v>112</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="N67" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>77</v>
@@ -10062,43 +10281,43 @@
         <v>77</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AC67" t="s" s="2">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="AD67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>511</v>
+        <v>118</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>201</v>
+        <v>77</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>512</v>
+        <v>108</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>384</v>
+        <v>77</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>77</v>
@@ -10106,12 +10325,14 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>513</v>
+        <v>483</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="C68" s="2"/>
+        <v>468</v>
+      </c>
+      <c r="C68" t="s" s="2">
+        <v>484</v>
+      </c>
       <c r="D68" t="s" s="2">
         <v>77</v>
       </c>
@@ -10120,7 +10341,7 @@
         <v>78</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>77</v>
@@ -10132,20 +10353,16 @@
         <v>77</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>514</v>
+        <v>111</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>515</v>
+        <v>485</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>518</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>77</v>
       </c>
@@ -10193,7 +10410,7 @@
         <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>513</v>
+        <v>118</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -10202,33 +10419,33 @@
         <v>79</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>519</v>
+        <v>77</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>520</v>
+        <v>119</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>521</v>
+        <v>77</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>522</v>
+        <v>77</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>523</v>
+        <v>77</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>524</v>
+        <v>486</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>524</v>
+        <v>487</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10242,27 +10459,25 @@
         <v>88</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>525</v>
+        <v>104</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>526</v>
+        <v>105</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>527</v>
+        <v>106</v>
       </c>
       <c r="N69" s="2"/>
-      <c r="O69" t="s" s="2">
-        <v>528</v>
-      </c>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>77</v>
       </c>
@@ -10310,7 +10525,7 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>524</v>
+        <v>107</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -10322,19 +10537,19 @@
         <v>77</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>403</v>
+        <v>77</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>529</v>
+        <v>108</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>77</v>
@@ -10342,10 +10557,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>530</v>
+        <v>488</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>530</v>
+        <v>489</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10356,7 +10571,7 @@
         <v>78</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>77</v>
@@ -10368,13 +10583,13 @@
         <v>77</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>105</v>
+        <v>203</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>106</v>
+        <v>204</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10413,31 +10628,31 @@
         <v>77</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AC70" t="s" s="2">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="AD70" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>77</v>
+        <v>119</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>77</v>
@@ -10446,7 +10661,7 @@
         <v>77</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>77</v>
@@ -10457,21 +10672,21 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>531</v>
+        <v>490</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>531</v>
+        <v>491</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>77</v>
@@ -10483,16 +10698,16 @@
         <v>77</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>111</v>
+        <v>133</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>112</v>
+        <v>255</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>113</v>
+        <v>256</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>114</v>
+        <v>257</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10500,7 +10715,7 @@
       </c>
       <c r="Q71" s="2"/>
       <c r="R71" t="s" s="2">
-        <v>77</v>
+        <v>484</v>
       </c>
       <c r="S71" t="s" s="2">
         <v>77</v>
@@ -10530,31 +10745,31 @@
         <v>77</v>
       </c>
       <c r="AB71" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AC71" t="s" s="2">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="AD71" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>118</v>
+        <v>259</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>77</v>
@@ -10563,7 +10778,7 @@
         <v>77</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>108</v>
+        <v>201</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>77</v>
@@ -10574,10 +10789,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>532</v>
+        <v>492</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>532</v>
+        <v>493</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10597,20 +10812,18 @@
         <v>77</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>104</v>
+        <v>343</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>533</v>
+        <v>263</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>535</v>
-      </c>
+        <v>264</v>
+      </c>
+      <c r="N72" s="2"/>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>77</v>
@@ -10635,13 +10848,11 @@
         <v>77</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y72" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="Y72" s="2"/>
       <c r="Z72" t="s" s="2">
-        <v>77</v>
+        <v>494</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>77</v>
@@ -10659,7 +10870,7 @@
         <v>77</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>536</v>
+        <v>265</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -10668,7 +10879,7 @@
         <v>88</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>537</v>
+        <v>77</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>101</v>
@@ -10691,12 +10902,14 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>538</v>
+        <v>495</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="C73" s="2"/>
+        <v>468</v>
+      </c>
+      <c r="C73" t="s" s="2">
+        <v>213</v>
+      </c>
       <c r="D73" t="s" s="2">
         <v>77</v>
       </c>
@@ -10714,20 +10927,18 @@
         <v>77</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>133</v>
+        <v>111</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>539</v>
+        <v>203</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>541</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="N73" s="2"/>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>77</v>
@@ -10752,11 +10963,13 @@
         <v>77</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="Y73" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="Z73" t="s" s="2">
-        <v>412</v>
+        <v>77</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>77</v>
@@ -10774,19 +10987,19 @@
         <v>77</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>542</v>
+        <v>118</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>77</v>
@@ -10795,7 +11008,7 @@
         <v>77</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>201</v>
+        <v>77</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>77</v>
@@ -10806,10 +11019,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>543</v>
+        <v>496</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>543</v>
+        <v>487</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10829,20 +11042,18 @@
         <v>77</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>313</v>
+        <v>104</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>544</v>
+        <v>105</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>546</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N74" s="2"/>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>77</v>
@@ -10891,7 +11102,7 @@
         <v>77</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>547</v>
+        <v>107</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -10903,7 +11114,7 @@
         <v>77</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>77</v>
@@ -10912,7 +11123,7 @@
         <v>77</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>548</v>
+        <v>108</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>77</v>
@@ -10923,10 +11134,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>549</v>
+        <v>497</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>549</v>
+        <v>489</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10937,7 +11148,7 @@
         <v>78</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>77</v>
@@ -10946,20 +11157,18 @@
         <v>77</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>550</v>
+        <v>203</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>552</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="N75" s="2"/>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>77</v>
@@ -10996,31 +11205,31 @@
         <v>77</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AC75" t="s" s="2">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="AD75" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>553</v>
+        <v>118</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>77</v>
@@ -11029,7 +11238,7 @@
         <v>77</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>201</v>
+        <v>77</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>77</v>
@@ -11040,10 +11249,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>554</v>
+        <v>498</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>554</v>
+        <v>491</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11051,10 +11260,10 @@
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>77</v>
@@ -11066,26 +11275,24 @@
         <v>77</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>555</v>
+        <v>133</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>556</v>
+        <v>255</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>557</v>
+        <v>256</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>559</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q76" s="2"/>
       <c r="R76" t="s" s="2">
-        <v>77</v>
+        <v>213</v>
       </c>
       <c r="S76" t="s" s="2">
         <v>77</v>
@@ -11127,19 +11334,19 @@
         <v>77</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>554</v>
+        <v>259</v>
       </c>
       <c r="AG76" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>77</v>
@@ -11148,7 +11355,7 @@
         <v>77</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>560</v>
+        <v>201</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>77</v>
@@ -11159,10 +11366,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>561</v>
+        <v>499</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>561</v>
+        <v>493</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11188,10 +11395,10 @@
         <v>104</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>105</v>
+        <v>263</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>106</v>
+        <v>264</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11242,7 +11449,7 @@
         <v>77</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>107</v>
+        <v>265</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -11254,7 +11461,7 @@
         <v>77</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>77</v>
@@ -11263,7 +11470,7 @@
         <v>77</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>108</v>
+        <v>201</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>77</v>
@@ -11274,21 +11481,23 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>562</v>
+        <v>500</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="C78" s="2"/>
+        <v>468</v>
+      </c>
+      <c r="C78" t="s" s="2">
+        <v>501</v>
+      </c>
       <c r="D78" t="s" s="2">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>77</v>
@@ -11303,14 +11512,12 @@
         <v>111</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>112</v>
+        <v>502</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="N78" s="2"/>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>77</v>
@@ -11380,7 +11587,7 @@
         <v>77</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>77</v>
@@ -11391,46 +11598,42 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>563</v>
+        <v>503</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>563</v>
+        <v>487</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>564</v>
+        <v>77</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I79" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>565</v>
+        <v>105</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>310</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N79" s="2"/>
+      <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>77</v>
       </c>
@@ -11478,19 +11681,19 @@
         <v>77</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>567</v>
+        <v>107</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>77</v>
@@ -11499,7 +11702,7 @@
         <v>77</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>201</v>
+        <v>108</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>77</v>
@@ -11510,10 +11713,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>568</v>
+        <v>504</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>568</v>
+        <v>489</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11524,7 +11727,7 @@
         <v>78</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>77</v>
@@ -11536,18 +11739,16 @@
         <v>77</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>343</v>
+        <v>111</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>569</v>
+        <v>203</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>570</v>
+        <v>204</v>
       </c>
       <c r="N80" s="2"/>
-      <c r="O80" t="s" s="2">
-        <v>571</v>
-      </c>
+      <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>77</v>
       </c>
@@ -11571,43 +11772,43 @@
         <v>77</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>154</v>
+        <v>77</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>572</v>
+        <v>77</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>573</v>
+        <v>77</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB80" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AC80" t="s" s="2">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="AD80" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE80" t="s" s="2">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>568</v>
+        <v>118</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>77</v>
@@ -11616,7 +11817,7 @@
         <v>77</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>574</v>
+        <v>77</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>77</v>
@@ -11627,10 +11828,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>575</v>
+        <v>505</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>575</v>
+        <v>491</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11638,7 +11839,7 @@
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G81" t="s" s="2">
         <v>88</v>
@@ -11653,24 +11854,24 @@
         <v>77</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>576</v>
+        <v>133</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>577</v>
+        <v>255</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="N81" s="2"/>
-      <c r="O81" t="s" s="2">
-        <v>579</v>
-      </c>
+        <v>256</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q81" s="2"/>
       <c r="R81" t="s" s="2">
-        <v>77</v>
+        <v>501</v>
       </c>
       <c r="S81" t="s" s="2">
         <v>77</v>
@@ -11712,10 +11913,10 @@
         <v>77</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>575</v>
+        <v>259</v>
       </c>
       <c r="AG81" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH81" t="s" s="2">
         <v>88</v>
@@ -11724,16 +11925,16 @@
         <v>77</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>580</v>
+        <v>77</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>581</v>
+        <v>201</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>77</v>
@@ -11744,10 +11945,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>582</v>
+        <v>506</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>582</v>
+        <v>493</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11758,7 +11959,7 @@
         <v>78</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>77</v>
@@ -11770,18 +11971,16 @@
         <v>77</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>438</v>
+        <v>104</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>583</v>
+        <v>263</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>584</v>
+        <v>264</v>
       </c>
       <c r="N82" s="2"/>
-      <c r="O82" t="s" s="2">
-        <v>585</v>
-      </c>
+      <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>77</v>
       </c>
@@ -11829,13 +12028,13 @@
         <v>77</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>582</v>
+        <v>265</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>77</v>
@@ -11847,10 +12046,10 @@
         <v>77</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>586</v>
+        <v>77</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>587</v>
+        <v>201</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>77</v>
@@ -11861,12 +12060,14 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>588</v>
+        <v>507</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="C83" s="2"/>
+        <v>468</v>
+      </c>
+      <c r="C83" t="s" s="2">
+        <v>508</v>
+      </c>
       <c r="D83" t="s" s="2">
         <v>77</v>
       </c>
@@ -11887,18 +12088,16 @@
         <v>77</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>514</v>
+        <v>111</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>589</v>
+        <v>203</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>590</v>
+        <v>204</v>
       </c>
       <c r="N83" s="2"/>
-      <c r="O83" t="s" s="2">
-        <v>591</v>
-      </c>
+      <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>77</v>
       </c>
@@ -11946,28 +12145,28 @@
         <v>77</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>588</v>
+        <v>118</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>592</v>
+        <v>77</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>593</v>
+        <v>77</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>77</v>
@@ -11978,10 +12177,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>594</v>
+        <v>509</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>594</v>
+        <v>487</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11992,7 +12191,7 @@
         <v>78</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>77</v>
@@ -12004,18 +12203,16 @@
         <v>77</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>595</v>
+        <v>104</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>596</v>
+        <v>105</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>597</v>
+        <v>106</v>
       </c>
       <c r="N84" s="2"/>
-      <c r="O84" t="s" s="2">
-        <v>598</v>
-      </c>
+      <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>77</v>
       </c>
@@ -12063,19 +12260,19 @@
         <v>77</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>594</v>
+        <v>107</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>77</v>
@@ -12093,8 +12290,4091 @@
         <v>77</v>
       </c>
     </row>
+    <row r="85" hidden="true">
+      <c r="A85" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="C85" s="2"/>
+      <c r="D85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E85" s="2"/>
+      <c r="F85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K85" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L85" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="M85" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="N85" s="2"/>
+      <c r="O85" s="2"/>
+      <c r="P85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q85" s="2"/>
+      <c r="R85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AF85" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AG85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ85" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO85" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="86" hidden="true">
+      <c r="A86" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="C86" s="2"/>
+      <c r="D86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E86" s="2"/>
+      <c r="F86" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G86" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K86" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L86" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="M86" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="O86" s="2"/>
+      <c r="P86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q86" s="2"/>
+      <c r="R86" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="S86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF86" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="AG86" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH86" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM86" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AN86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO86" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="87" hidden="true">
+      <c r="A87" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="B87" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="C87" s="2"/>
+      <c r="D87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E87" s="2"/>
+      <c r="F87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G87" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K87" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L87" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="M87" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="N87" s="2"/>
+      <c r="O87" s="2"/>
+      <c r="P87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q87" s="2"/>
+      <c r="R87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF87" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="AG87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH87" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ87" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM87" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AN87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO87" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="88" hidden="true">
+      <c r="A88" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="C88" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="D88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E88" s="2"/>
+      <c r="F88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G88" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K88" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L88" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="N88" s="2"/>
+      <c r="O88" s="2"/>
+      <c r="P88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q88" s="2"/>
+      <c r="R88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF88" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AG88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ88" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO88" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="89" hidden="true">
+      <c r="A89" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="B89" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="C89" s="2"/>
+      <c r="D89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E89" s="2"/>
+      <c r="F89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G89" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K89" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L89" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="M89" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="N89" s="2"/>
+      <c r="O89" s="2"/>
+      <c r="P89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q89" s="2"/>
+      <c r="R89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF89" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AG89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH89" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM89" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AN89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO89" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="90" hidden="true">
+      <c r="A90" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="B90" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="C90" s="2"/>
+      <c r="D90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E90" s="2"/>
+      <c r="F90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K90" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L90" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="N90" s="2"/>
+      <c r="O90" s="2"/>
+      <c r="P90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q90" s="2"/>
+      <c r="R90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AF90" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AG90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH90" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ90" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO90" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="91" hidden="true">
+      <c r="A91" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="B91" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="C91" s="2"/>
+      <c r="D91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E91" s="2"/>
+      <c r="F91" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G91" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K91" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L91" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="N91" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="O91" s="2"/>
+      <c r="P91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q91" s="2"/>
+      <c r="R91" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="S91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF91" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="AG91" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH91" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM91" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AN91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO91" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="92" hidden="true">
+      <c r="A92" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="B92" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="C92" s="2"/>
+      <c r="D92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E92" s="2"/>
+      <c r="F92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G92" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K92" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="L92" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="M92" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="N92" s="2"/>
+      <c r="O92" s="2"/>
+      <c r="P92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q92" s="2"/>
+      <c r="R92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF92" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="AG92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH92" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ92" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM92" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AN92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO92" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="93" hidden="true">
+      <c r="A93" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="B93" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="C93" s="2"/>
+      <c r="D93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E93" s="2"/>
+      <c r="F93" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G93" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K93" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L93" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="O93" s="2"/>
+      <c r="P93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q93" s="2"/>
+      <c r="R93" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="S93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF93" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="AG93" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH93" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM93" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AN93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO93" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="94" hidden="true">
+      <c r="A94" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="B94" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="C94" s="2"/>
+      <c r="D94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E94" s="2"/>
+      <c r="F94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K94" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="L94" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="M94" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="N94" s="2"/>
+      <c r="O94" s="2"/>
+      <c r="P94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q94" s="2"/>
+      <c r="R94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF94" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="AG94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH94" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ94" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM94" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AN94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO94" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="B95" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="C95" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="D95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E95" s="2"/>
+      <c r="F95" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G95" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H95" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K95" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="L95" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="M95" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="N95" s="2"/>
+      <c r="O95" s="2"/>
+      <c r="P95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q95" s="2"/>
+      <c r="R95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF95" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AG95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ95" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO95" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="B96" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="C96" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="D96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E96" s="2"/>
+      <c r="F96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G96" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H96" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K96" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="L96" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="M96" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="N96" s="2"/>
+      <c r="O96" s="2"/>
+      <c r="P96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q96" s="2"/>
+      <c r="R96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF96" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AG96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH96" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ96" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO96" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="C97" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="D97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E97" s="2"/>
+      <c r="F97" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G97" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H97" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K97" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="L97" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="N97" s="2"/>
+      <c r="O97" s="2"/>
+      <c r="P97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q97" s="2"/>
+      <c r="R97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF97" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AG97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH97" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ97" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO97" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="98" hidden="true">
+      <c r="A98" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="C98" s="2"/>
+      <c r="D98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E98" s="2"/>
+      <c r="F98" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G98" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J98" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K98" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="L98" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="M98" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="N98" s="2"/>
+      <c r="O98" s="2"/>
+      <c r="P98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q98" s="2"/>
+      <c r="R98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S98" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="T98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X98" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="Y98" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="Z98" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="AA98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF98" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="AG98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH98" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI98" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="AJ98" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL98" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="AM98" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="AN98" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="AO98" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="B99" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="C99" s="2"/>
+      <c r="D99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E99" s="2"/>
+      <c r="F99" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G99" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H99" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J99" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K99" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L99" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="M99" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="N99" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="O99" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="P99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q99" s="2"/>
+      <c r="R99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF99" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="AG99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH99" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ99" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK99" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="AL99" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="AM99" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="AN99" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="AO99" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="100" hidden="true">
+      <c r="A100" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="C100" s="2"/>
+      <c r="D100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E100" s="2"/>
+      <c r="F100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G100" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I100" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="J100" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K100" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="L100" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="M100" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="O100" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="P100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q100" s="2"/>
+      <c r="R100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X100" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="Y100" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="Z100" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="AA100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF100" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="AG100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH100" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ100" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL100" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="AM100" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="AN100" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="AO100" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="101" hidden="true">
+      <c r="A101" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="B101" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="C101" s="2"/>
+      <c r="D101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E101" s="2"/>
+      <c r="F101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G101" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J101" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K101" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="L101" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="O101" s="2"/>
+      <c r="P101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q101" s="2"/>
+      <c r="R101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF101" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="AG101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH101" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ101" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL101" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AM101" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AN101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO101" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="102" hidden="true">
+      <c r="A102" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="B102" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="C102" s="2"/>
+      <c r="D102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E102" s="2"/>
+      <c r="F102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G102" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J102" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K102" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="L102" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="M102" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="N102" s="2"/>
+      <c r="O102" s="2"/>
+      <c r="P102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q102" s="2"/>
+      <c r="R102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF102" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="AG102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH102" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ102" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL102" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AM102" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="AN102" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AO102" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="103" hidden="true">
+      <c r="A103" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="C103" s="2"/>
+      <c r="D103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E103" s="2"/>
+      <c r="F103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K103" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="L103" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="M103" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="O103" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="P103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q103" s="2"/>
+      <c r="R103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF103" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="AG103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI103" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="AJ103" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="AK103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL103" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="AM103" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="AN103" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="AO103" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="B104" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="C104" s="2"/>
+      <c r="D104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E104" s="2"/>
+      <c r="F104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G104" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H104" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J104" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K104" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="L104" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="M104" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="N104" s="2"/>
+      <c r="O104" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="P104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q104" s="2"/>
+      <c r="R104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF104" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="AG104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH104" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ104" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL104" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AM104" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="AN104" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AO104" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="105" hidden="true">
+      <c r="A105" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="B105" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="C105" s="2"/>
+      <c r="D105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E105" s="2"/>
+      <c r="F105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G105" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K105" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L105" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="M105" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="N105" s="2"/>
+      <c r="O105" s="2"/>
+      <c r="P105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q105" s="2"/>
+      <c r="R105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF105" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AG105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH105" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM105" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AN105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO105" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="106" hidden="true">
+      <c r="A106" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="B106" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="C106" s="2"/>
+      <c r="D106" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="E106" s="2"/>
+      <c r="F106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K106" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L106" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="M106" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="N106" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O106" s="2"/>
+      <c r="P106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q106" s="2"/>
+      <c r="R106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB106" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AC106" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AD106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE106" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AF106" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AG106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ106" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM106" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AN106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO106" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="107" hidden="true">
+      <c r="A107" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="B107" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="C107" s="2"/>
+      <c r="D107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E107" s="2"/>
+      <c r="F107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G107" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J107" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K107" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L107" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="M107" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="N107" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="O107" s="2"/>
+      <c r="P107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q107" s="2"/>
+      <c r="R107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF107" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="AG107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH107" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI107" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="AJ107" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM107" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AN107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO107" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="108" hidden="true">
+      <c r="A108" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="B108" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="C108" s="2"/>
+      <c r="D108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E108" s="2"/>
+      <c r="F108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G108" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J108" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K108" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L108" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="M108" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="N108" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="O108" s="2"/>
+      <c r="P108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q108" s="2"/>
+      <c r="R108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X108" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="Y108" s="2"/>
+      <c r="Z108" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="AA108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF108" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="AG108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH108" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ108" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM108" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AN108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO108" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="109" hidden="true">
+      <c r="A109" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="B109" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="C109" s="2"/>
+      <c r="D109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E109" s="2"/>
+      <c r="F109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G109" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J109" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K109" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="L109" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="M109" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="N109" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="O109" s="2"/>
+      <c r="P109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q109" s="2"/>
+      <c r="R109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF109" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="AG109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH109" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ109" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM109" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="AN109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO109" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="110" hidden="true">
+      <c r="A110" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="B110" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="C110" s="2"/>
+      <c r="D110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E110" s="2"/>
+      <c r="F110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G110" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J110" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K110" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L110" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="M110" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="N110" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="O110" s="2"/>
+      <c r="P110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q110" s="2"/>
+      <c r="R110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF110" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="AG110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH110" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ110" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM110" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AN110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO110" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="111" hidden="true">
+      <c r="A111" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="B111" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="C111" s="2"/>
+      <c r="D111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E111" s="2"/>
+      <c r="F111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G111" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K111" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="L111" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="M111" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="N111" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="O111" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="P111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q111" s="2"/>
+      <c r="R111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF111" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="AG111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH111" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ111" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM111" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="AN111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO111" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="112" hidden="true">
+      <c r="A112" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="B112" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="C112" s="2"/>
+      <c r="D112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E112" s="2"/>
+      <c r="F112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G112" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K112" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L112" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="M112" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="N112" s="2"/>
+      <c r="O112" s="2"/>
+      <c r="P112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q112" s="2"/>
+      <c r="R112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF112" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AG112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH112" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM112" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AN112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO112" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="113" hidden="true">
+      <c r="A113" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="B113" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="C113" s="2"/>
+      <c r="D113" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="E113" s="2"/>
+      <c r="F113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G113" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K113" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L113" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="M113" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="N113" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O113" s="2"/>
+      <c r="P113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q113" s="2"/>
+      <c r="R113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF113" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AG113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH113" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ113" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM113" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AN113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO113" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="114" hidden="true">
+      <c r="A114" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="B114" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="C114" s="2"/>
+      <c r="D114" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="E114" s="2"/>
+      <c r="F114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G114" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I114" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="J114" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K114" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L114" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="M114" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="N114" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O114" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="P114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q114" s="2"/>
+      <c r="R114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF114" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="AG114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH114" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ114" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM114" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AN114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO114" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="115" hidden="true">
+      <c r="A115" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="B115" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="C115" s="2"/>
+      <c r="D115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E115" s="2"/>
+      <c r="F115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G115" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K115" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="L115" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="M115" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="N115" s="2"/>
+      <c r="O115" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="P115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q115" s="2"/>
+      <c r="R115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X115" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="Y115" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="Z115" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="AA115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF115" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="AG115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH115" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ115" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM115" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="AN115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO115" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="116" hidden="true">
+      <c r="A116" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="B116" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="C116" s="2"/>
+      <c r="D116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E116" s="2"/>
+      <c r="F116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G116" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K116" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="L116" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="M116" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="N116" s="2"/>
+      <c r="O116" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="P116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q116" s="2"/>
+      <c r="R116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF116" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="AG116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH116" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ116" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL116" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="AM116" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="AN116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO116" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="117" hidden="true">
+      <c r="A117" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="B117" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="C117" s="2"/>
+      <c r="D117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E117" s="2"/>
+      <c r="F117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G117" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K117" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="L117" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="M117" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="N117" s="2"/>
+      <c r="O117" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="P117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q117" s="2"/>
+      <c r="R117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF117" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="AG117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH117" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ117" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL117" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="AM117" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="AN117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO117" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="118" hidden="true">
+      <c r="A118" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="B118" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="C118" s="2"/>
+      <c r="D118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E118" s="2"/>
+      <c r="F118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G118" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K118" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="L118" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="M118" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="N118" s="2"/>
+      <c r="O118" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="P118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q118" s="2"/>
+      <c r="R118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF118" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="AG118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH118" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ118" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL118" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="AM118" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="AN118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO118" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="119" hidden="true">
+      <c r="A119" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="B119" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="C119" s="2"/>
+      <c r="D119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E119" s="2"/>
+      <c r="F119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G119" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K119" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="L119" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="M119" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="N119" s="2"/>
+      <c r="O119" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="P119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q119" s="2"/>
+      <c r="R119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF119" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="AG119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH119" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ119" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM119" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AN119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO119" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AO84">
+  <autoFilter ref="A1:AO119">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -12104,7 +16384,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI83">
+  <conditionalFormatting sqref="A2:AI118">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/update-dependencies-fr-core-annuaire/ig/StructureDefinition-ror-internal-organization.xlsx
+++ b/update-dependencies-fr-core-annuaire/ig/StructureDefinition-ror-internal-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T14:30:36+00:00</t>
+    <t>2026-08-21T16:03:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/update-dependencies-fr-core-annuaire/ig/StructureDefinition-ror-internal-organization.xlsx
+++ b/update-dependencies-fr-core-annuaire/ig/StructureDefinition-ror-internal-organization.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4425" uniqueCount="671">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4425" uniqueCount="673">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T16:03:39+00:00</t>
+    <t>2026-08-26T13:04:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -706,6 +706,136 @@
     <t>The date range that this organization should be considered available.</t>
   </si>
   <si>
+    <t>Organization.extension:usePeriod.id</t>
+  </si>
+  <si>
+    <t>Organization.extension.id</t>
+  </si>
+  <si>
+    <t>Organization.extension:usePeriod.extension</t>
+  </si>
+  <si>
+    <t>Organization.extension.extension</t>
+  </si>
+  <si>
+    <t>Organization.extension:usePeriod.url</t>
+  </si>
+  <si>
+    <t>Organization.extension.url</t>
+  </si>
+  <si>
+    <t>identifies the meaning of the extension</t>
+  </si>
+  <si>
+    <t>Source of the definition for the extension code - a logical name or a URL.</t>
+  </si>
+  <si>
+    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/StructureDefinition/organization-period</t>
+  </si>
+  <si>
+    <t>Extension.url</t>
+  </si>
+  <si>
+    <t>Organization.extension:usePeriod.value[x]</t>
+  </si>
+  <si>
+    <t>Organization.extension.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
+</t>
+  </si>
+  <si>
+    <t>Value of extension</t>
+  </si>
+  <si>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R5/extensibility.html) for a list).</t>
+  </si>
+  <si>
+    <t>Extension.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ext-1
+</t>
+  </si>
+  <si>
+    <t>Organization.extension:usePeriod.value[x].id</t>
+  </si>
+  <si>
+    <t>Organization.extension.value[x].id</t>
+  </si>
+  <si>
+    <t>Organization.extension:usePeriod.value[x].extension</t>
+  </si>
+  <si>
+    <t>Organization.extension.value[x].extension</t>
+  </si>
+  <si>
+    <t>Organization.extension:usePeriod.value[x].start</t>
+  </si>
+  <si>
+    <t>Organization.extension.value[x].start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>Starting time with inclusive boundary</t>
+  </si>
+  <si>
+    <t>The start of the period. The boundary is inclusive.</t>
+  </si>
+  <si>
+    <t>If the low element is missing, the meaning is that the low boundary is not known.</t>
+  </si>
+  <si>
+    <t>Period.start</t>
+  </si>
+  <si>
+    <t>ele-1
+per-1</t>
+  </si>
+  <si>
+    <t>DR.1</t>
+  </si>
+  <si>
+    <t>./low</t>
+  </si>
+  <si>
+    <t>Organization.extension:usePeriod.value[x].end</t>
+  </si>
+  <si>
+    <t>Organization.extension.value[x].end</t>
+  </si>
+  <si>
+    <t>End time with inclusive boundary, if not ongoing</t>
+  </si>
+  <si>
+    <t>The end of the period. If the end of the period is missing, it means no end was known or planned at the time the instance was created. The start may be in the past, and the end date in the future, which means that period is expected/planned to end at that time.</t>
+  </si>
+  <si>
+    <t>The high value includes any matching date/time. i.e. 2012-02-03T10:00:00 is in a period that has an end value of 2012-02-03.</t>
+  </si>
+  <si>
+    <t>If the end of the period is missing, it means that the period is ongoing</t>
+  </si>
+  <si>
+    <t>Period.end</t>
+  </si>
+  <si>
+    <t>dateOuverture</t>
+  </si>
+  <si>
+    <t>DR.2</t>
+  </si>
+  <si>
+    <t>./high</t>
+  </si>
+  <si>
     <t>Organization.extension:openReason</t>
   </si>
   <si>
@@ -793,132 +923,6 @@
   </si>
   <si>
     <t>dateOuverture (OI) + dateFermeture (OI)</t>
-  </si>
-  <si>
-    <t>Organization.extension:organization-period.id</t>
-  </si>
-  <si>
-    <t>Organization.extension.id</t>
-  </si>
-  <si>
-    <t>Organization.extension:organization-period.extension</t>
-  </si>
-  <si>
-    <t>Organization.extension.extension</t>
-  </si>
-  <si>
-    <t>Organization.extension:organization-period.url</t>
-  </si>
-  <si>
-    <t>Organization.extension.url</t>
-  </si>
-  <si>
-    <t>identifies the meaning of the extension</t>
-  </si>
-  <si>
-    <t>Source of the definition for the extension code - a logical name or a URL.</t>
-  </si>
-  <si>
-    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/StructureDefinition/organization-period</t>
-  </si>
-  <si>
-    <t>Extension.url</t>
-  </si>
-  <si>
-    <t>Organization.extension:organization-period.value[x]</t>
-  </si>
-  <si>
-    <t>Organization.extension.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Period
-</t>
-  </si>
-  <si>
-    <t>Value of extension</t>
-  </si>
-  <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
-  </si>
-  <si>
-    <t>Extension.value[x]</t>
-  </si>
-  <si>
-    <t>Organization.extension:organization-period.value[x].id</t>
-  </si>
-  <si>
-    <t>Organization.extension.value[x].id</t>
-  </si>
-  <si>
-    <t>Organization.extension:organization-period.value[x].extension</t>
-  </si>
-  <si>
-    <t>Organization.extension.value[x].extension</t>
-  </si>
-  <si>
-    <t>Organization.extension:organization-period.value[x].start</t>
-  </si>
-  <si>
-    <t>Organization.extension.value[x].start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dateTime
-</t>
-  </si>
-  <si>
-    <t>Starting time with inclusive boundary</t>
-  </si>
-  <si>
-    <t>The start of the period. The boundary is inclusive.</t>
-  </si>
-  <si>
-    <t>If the low element is missing, the meaning is that the low boundary is not known.</t>
-  </si>
-  <si>
-    <t>Period.start</t>
-  </si>
-  <si>
-    <t>ele-1
-per-1</t>
-  </si>
-  <si>
-    <t>DR.1</t>
-  </si>
-  <si>
-    <t>./low</t>
-  </si>
-  <si>
-    <t>Organization.extension:organization-period.value[x].end</t>
-  </si>
-  <si>
-    <t>Organization.extension.value[x].end</t>
-  </si>
-  <si>
-    <t>End time with inclusive boundary, if not ongoing</t>
-  </si>
-  <si>
-    <t>The end of the period. If the end of the period is missing, it means no end was known or planned at the time the instance was created. The start may be in the past, and the end date in the future, which means that period is expected/planned to end at that time.</t>
-  </si>
-  <si>
-    <t>The high value includes any matching date/time. i.e. 2012-02-03T10:00:00 is in a period that has an end value of 2012-02-03.</t>
-  </si>
-  <si>
-    <t>If the end of the period is missing, it means that the period is ongoing</t>
-  </si>
-  <si>
-    <t>Period.end</t>
-  </si>
-  <si>
-    <t>dateOuverture</t>
-  </si>
-  <si>
-    <t>DR.2</t>
-  </si>
-  <si>
-    <t>./high</t>
   </si>
   <si>
     <t>Organization.extension:ror-meta-comment</t>
@@ -1502,6 +1506,9 @@
   </si>
   <si>
     <t>Organization.telecom.extension.value[x]</t>
+  </si>
+  <si>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
   </si>
   <si>
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
@@ -5057,11 +5064,9 @@
         <v>221</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="C23" t="s" s="2">
         <v>222</v>
       </c>
+      <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
         <v>77</v>
       </c>
@@ -5082,17 +5087,15 @@
         <v>77</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>223</v>
+        <v>90</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>224</v>
+        <v>105</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>225</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>77</v>
@@ -5141,19 +5144,19 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>205</v>
+        <v>107</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>77</v>
+        <v>211</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>77</v>
@@ -5162,7 +5165,7 @@
         <v>77</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>77</v>
@@ -5173,14 +5176,12 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="C24" t="s" s="2">
-        <v>227</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
         <v>77</v>
       </c>
@@ -5189,7 +5190,7 @@
         <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>77</v>
@@ -5201,17 +5202,15 @@
         <v>77</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>223</v>
+        <v>111</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>224</v>
+        <v>203</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>225</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>77</v>
@@ -5248,19 +5247,19 @@
         <v>77</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>205</v>
+        <v>118</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -5292,23 +5291,21 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="C25" t="s" s="2">
-        <v>229</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>77</v>
@@ -5320,22 +5317,24 @@
         <v>77</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>230</v>
+        <v>133</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="N25" s="2"/>
+        <v>228</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>77</v>
+        <v>230</v>
       </c>
       <c r="S25" t="s" s="2">
         <v>77</v>
@@ -5377,19 +5376,19 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>205</v>
+        <v>231</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>211</v>
+        <v>77</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>77</v>
@@ -5398,7 +5397,7 @@
         <v>77</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>77</v>
+        <v>201</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>77</v>
@@ -5407,28 +5406,26 @@
         <v>77</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="B26" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="B26" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="C26" t="s" s="2">
-        <v>234</v>
-      </c>
+      <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>77</v>
@@ -5437,13 +5434,13 @@
         <v>77</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="M26" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5494,28 +5491,28 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>205</v>
+        <v>237</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>77</v>
+        <v>238</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>238</v>
+        <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>77</v>
+        <v>201</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>77</v>
@@ -5524,16 +5521,14 @@
         <v>77</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
         <v>239</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="C27" t="s" s="2">
         <v>240</v>
       </c>
+      <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
         <v>77</v>
       </c>
@@ -5545,7 +5540,7 @@
         <v>88</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>77</v>
@@ -5554,13 +5549,13 @@
         <v>77</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>241</v>
+        <v>104</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>242</v>
+        <v>105</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>243</v>
+        <v>106</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -5611,28 +5606,28 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>205</v>
+        <v>107</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>244</v>
+        <v>77</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>77</v>
@@ -5641,28 +5636,26 @@
         <v>77</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="C28" t="s" s="2">
-        <v>246</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>77</v>
@@ -5671,15 +5664,17 @@
         <v>77</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>247</v>
+        <v>111</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>248</v>
+        <v>112</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>77</v>
@@ -5716,19 +5711,19 @@
         <v>77</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>205</v>
+        <v>118</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -5737,7 +5732,7 @@
         <v>79</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>77</v>
+        <v>211</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>119</v>
@@ -5749,7 +5744,7 @@
         <v>77</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>77</v>
+        <v>201</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>77</v>
@@ -5760,10 +5755,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5783,18 +5778,20 @@
         <v>77</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>104</v>
+        <v>245</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>105</v>
+        <v>246</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N29" s="2"/>
+        <v>247</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>248</v>
+      </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>77</v>
@@ -5843,7 +5840,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>107</v>
+        <v>249</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5852,19 +5849,19 @@
         <v>88</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>77</v>
+        <v>250</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>77</v>
+        <v>251</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>108</v>
+        <v>252</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>77</v>
@@ -5875,10 +5872,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5889,7 +5886,7 @@
         <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>77</v>
@@ -5898,23 +5895,27 @@
         <v>77</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>111</v>
+        <v>245</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>203</v>
+        <v>255</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>256</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>257</v>
+      </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q30" s="2"/>
+      <c r="Q30" t="s" s="2">
+        <v>258</v>
+      </c>
       <c r="R30" t="s" s="2">
         <v>77</v>
       </c>
@@ -5946,40 +5947,40 @@
         <v>77</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>118</v>
+        <v>259</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>77</v>
+        <v>250</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>77</v>
+        <v>260</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>77</v>
+        <v>261</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>77</v>
+        <v>262</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>77</v>
@@ -5990,18 +5991,20 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="C31" s="2"/>
+        <v>202</v>
+      </c>
+      <c r="C31" t="s" s="2">
+        <v>264</v>
+      </c>
       <c r="D31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>88</v>
@@ -6016,16 +6019,16 @@
         <v>77</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>133</v>
+        <v>265</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -6033,7 +6036,7 @@
       </c>
       <c r="Q31" s="2"/>
       <c r="R31" t="s" s="2">
-        <v>258</v>
+        <v>77</v>
       </c>
       <c r="S31" t="s" s="2">
         <v>77</v>
@@ -6075,19 +6078,19 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>259</v>
+        <v>205</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>77</v>
+        <v>119</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>77</v>
@@ -6096,7 +6099,7 @@
         <v>77</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>201</v>
+        <v>77</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>77</v>
@@ -6107,18 +6110,20 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="C32" s="2"/>
+        <v>202</v>
+      </c>
+      <c r="C32" t="s" s="2">
+        <v>269</v>
+      </c>
       <c r="D32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>88</v>
@@ -6133,15 +6138,17 @@
         <v>77</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>266</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>267</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>77</v>
@@ -6190,19 +6197,19 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>265</v>
+        <v>205</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>77</v>
@@ -6211,7 +6218,7 @@
         <v>77</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>201</v>
+        <v>77</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>77</v>
@@ -6222,12 +6229,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="C33" s="2"/>
+        <v>202</v>
+      </c>
+      <c r="C33" t="s" s="2">
+        <v>271</v>
+      </c>
       <c r="D33" t="s" s="2">
         <v>77</v>
       </c>
@@ -6236,7 +6245,7 @@
         <v>78</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>77</v>
@@ -6248,13 +6257,13 @@
         <v>77</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>104</v>
+        <v>272</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>105</v>
+        <v>273</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>106</v>
+        <v>274</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6305,19 +6314,19 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>107</v>
+        <v>205</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>77</v>
+        <v>211</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>77</v>
+        <v>119</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>77</v>
@@ -6326,7 +6335,7 @@
         <v>77</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>77</v>
@@ -6335,26 +6344,28 @@
         <v>77</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="C34" s="2"/>
+        <v>202</v>
+      </c>
+      <c r="C34" t="s" s="2">
+        <v>276</v>
+      </c>
       <c r="D34" t="s" s="2">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>77</v>
@@ -6363,17 +6374,15 @@
         <v>77</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>111</v>
+        <v>277</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>112</v>
+        <v>278</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>279</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>77</v>
@@ -6410,19 +6419,19 @@
         <v>77</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="AD34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>118</v>
+        <v>205</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -6431,19 +6440,19 @@
         <v>79</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>211</v>
+        <v>77</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>119</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>77</v>
+        <v>280</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>201</v>
+        <v>77</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>77</v>
@@ -6452,14 +6461,16 @@
         <v>77</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="C35" s="2"/>
+        <v>202</v>
+      </c>
+      <c r="C35" t="s" s="2">
+        <v>282</v>
+      </c>
       <c r="D35" t="s" s="2">
         <v>77</v>
       </c>
@@ -6471,26 +6482,24 @@
         <v>88</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>275</v>
-      </c>
+        <v>285</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>77</v>
@@ -6539,28 +6548,28 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>276</v>
+        <v>205</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>277</v>
+        <v>77</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>77</v>
+        <v>286</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>278</v>
+        <v>77</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>279</v>
+        <v>77</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>77</v>
@@ -6569,14 +6578,16 @@
         <v>77</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="C36" s="2"/>
+        <v>202</v>
+      </c>
+      <c r="C36" t="s" s="2">
+        <v>288</v>
+      </c>
       <c r="D36" t="s" s="2">
         <v>77</v>
       </c>
@@ -6588,33 +6599,29 @@
         <v>88</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>272</v>
+        <v>289</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>284</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q36" t="s" s="2">
-        <v>285</v>
-      </c>
+      <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
         <v>77</v>
       </c>
@@ -6658,28 +6665,28 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>286</v>
+        <v>205</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>277</v>
+        <v>77</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>287</v>
+        <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>288</v>
+        <v>77</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>289</v>
+        <v>77</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>77</v>
@@ -6690,13 +6697,13 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>202</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D37" t="s" s="2">
         <v>77</v>
@@ -6718,13 +6725,13 @@
         <v>77</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6807,13 +6814,13 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>202</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D38" t="s" s="2">
         <v>77</v>
@@ -6835,13 +6842,13 @@
         <v>77</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6907,7 +6914,7 @@
         <v>119</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>77</v>
@@ -6924,13 +6931,13 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>202</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D39" t="s" s="2">
         <v>77</v>
@@ -6952,13 +6959,13 @@
         <v>77</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -7024,7 +7031,7 @@
         <v>119</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>77</v>
@@ -7041,10 +7048,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7070,16 +7077,16 @@
         <v>111</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="N40" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>77</v>
@@ -7128,7 +7135,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -7160,10 +7167,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7186,17 +7193,17 @@
         <v>89</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>77</v>
@@ -7233,7 +7240,7 @@
         <v>77</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AC41" s="2"/>
       <c r="AD41" t="s" s="2">
@@ -7243,7 +7250,7 @@
         <v>117</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -7252,7 +7259,7 @@
         <v>79</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>101</v>
@@ -7261,27 +7268,27 @@
         <v>77</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D42" t="s" s="2">
         <v>77</v>
@@ -7303,17 +7310,17 @@
         <v>89</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>77</v>
@@ -7362,7 +7369,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -7371,33 +7378,33 @@
         <v>79</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7509,10 +7516,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7626,10 +7633,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7655,16 +7662,16 @@
         <v>178</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>77</v>
@@ -7692,10 +7699,10 @@
         <v>169</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>77</v>
@@ -7713,7 +7720,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7734,7 +7741,7 @@
         <v>201</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>77</v>
@@ -7745,10 +7752,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7771,19 +7778,19 @@
         <v>89</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>77</v>
@@ -7793,7 +7800,7 @@
         <v>77</v>
       </c>
       <c r="S46" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="T46" t="s" s="2">
         <v>77</v>
@@ -7811,10 +7818,10 @@
         <v>154</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>77</v>
@@ -7832,7 +7839,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7850,10 +7857,10 @@
         <v>77</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>77</v>
@@ -7864,10 +7871,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7893,16 +7900,16 @@
         <v>133</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>77</v>
@@ -7912,10 +7919,10 @@
         <v>77</v>
       </c>
       <c r="S47" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="T47" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="U47" t="s" s="2">
         <v>77</v>
@@ -7951,7 +7958,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7969,13 +7976,13 @@
         <v>77</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>77</v>
@@ -7983,10 +7990,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8012,13 +8019,13 @@
         <v>104</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8032,7 +8039,7 @@
         <v>77</v>
       </c>
       <c r="T48" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="U48" t="s" s="2">
         <v>77</v>
@@ -8068,7 +8075,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -8086,13 +8093,13 @@
         <v>77</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>77</v>
@@ -8100,10 +8107,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8126,16 +8133,16 @@
         <v>89</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>262</v>
+        <v>234</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8185,7 +8192,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -8197,19 +8204,19 @@
         <v>211</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>77</v>
@@ -8217,10 +8224,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8243,16 +8250,16 @@
         <v>89</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8302,7 +8309,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -8314,19 +8321,19 @@
         <v>211</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>77</v>
@@ -8334,10 +8341,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8360,70 +8367,70 @@
         <v>89</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="P51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q51" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="R51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF51" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="L51" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="P51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q51" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="R51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF51" t="s" s="2">
-        <v>396</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -8441,24 +8448,24 @@
         <v>77</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8481,19 +8488,19 @@
         <v>89</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>77</v>
@@ -8522,16 +8529,16 @@
       </c>
       <c r="Y52" s="2"/>
       <c r="Z52" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>77</v>
@@ -8540,7 +8547,7 @@
         <v>117</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -8558,27 +8565,27 @@
         <v>77</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>108</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D53" t="s" s="2">
         <v>77</v>
@@ -8600,19 +8607,19 @@
         <v>89</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>77</v>
@@ -8641,7 +8648,7 @@
       </c>
       <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>77</v>
@@ -8659,7 +8666,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8674,27 +8681,27 @@
         <v>101</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>108</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8720,16 +8727,16 @@
         <v>104</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>77</v>
@@ -8778,7 +8785,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8787,22 +8794,22 @@
         <v>88</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>77</v>
@@ -8810,10 +8817,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8839,16 +8846,16 @@
         <v>104</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>77</v>
@@ -8897,7 +8904,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8918,7 +8925,7 @@
         <v>77</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>77</v>
@@ -8929,10 +8936,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8955,19 +8962,19 @@
         <v>77</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>77</v>
@@ -9004,10 +9011,10 @@
         <v>77</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AC56" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AD56" t="s" s="2">
         <v>77</v>
@@ -9016,7 +9023,7 @@
         <v>117</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -9025,22 +9032,22 @@
         <v>79</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>77</v>
@@ -9048,13 +9055,13 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D57" t="s" s="2">
         <v>77</v>
@@ -9076,19 +9083,19 @@
         <v>77</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>77</v>
@@ -9137,7 +9144,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -9146,22 +9153,22 @@
         <v>79</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>77</v>
@@ -9169,10 +9176,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9284,10 +9291,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9295,7 +9302,7 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="G59" t="s" s="2">
         <v>79</v>
@@ -9399,13 +9406,13 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D60" t="s" s="2">
         <v>77</v>
@@ -9427,13 +9434,13 @@
         <v>77</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9516,10 +9523,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9631,10 +9638,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9746,10 +9753,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9775,13 +9782,13 @@
         <v>133</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>255</v>
+        <v>227</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>256</v>
+        <v>228</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>257</v>
+        <v>229</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9789,7 +9796,7 @@
       </c>
       <c r="Q63" s="2"/>
       <c r="R63" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="S63" t="s" s="2">
         <v>77</v>
@@ -9831,7 +9838,7 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>259</v>
+        <v>231</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>88</v>
@@ -9863,10 +9870,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9892,10 +9899,10 @@
         <v>150</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>263</v>
+        <v>235</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>264</v>
+        <v>475</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9907,7 +9914,7 @@
         <v>77</v>
       </c>
       <c r="S64" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="T64" t="s" s="2">
         <v>77</v>
@@ -9926,7 +9933,7 @@
       </c>
       <c r="Y64" s="2"/>
       <c r="Z64" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>77</v>
@@ -9944,7 +9951,7 @@
         <v>77</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>265</v>
+        <v>237</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9976,13 +9983,13 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="D65" t="s" s="2">
         <v>77</v>
@@ -10004,13 +10011,13 @@
         <v>77</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -10093,10 +10100,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10208,10 +10215,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10325,13 +10332,13 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="D68" t="s" s="2">
         <v>77</v>
@@ -10356,7 +10363,7 @@
         <v>111</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="M68" t="s" s="2">
         <v>204</v>
@@ -10442,10 +10449,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10557,10 +10564,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10672,10 +10679,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10701,13 +10708,13 @@
         <v>133</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>255</v>
+        <v>227</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>256</v>
+        <v>228</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>257</v>
+        <v>229</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10715,7 +10722,7 @@
       </c>
       <c r="Q71" s="2"/>
       <c r="R71" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="S71" t="s" s="2">
         <v>77</v>
@@ -10757,7 +10764,7 @@
         <v>77</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>259</v>
+        <v>231</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>88</v>
@@ -10789,10 +10796,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10815,13 +10822,13 @@
         <v>77</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>263</v>
+        <v>235</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>264</v>
+        <v>475</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10852,7 +10859,7 @@
       </c>
       <c r="Y72" s="2"/>
       <c r="Z72" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>77</v>
@@ -10870,7 +10877,7 @@
         <v>77</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>265</v>
+        <v>237</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -10902,10 +10909,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C73" t="s" s="2">
         <v>213</v>
@@ -11019,10 +11026,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11134,10 +11141,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11249,10 +11256,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11278,13 +11285,13 @@
         <v>133</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>255</v>
+        <v>227</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>256</v>
+        <v>228</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>257</v>
+        <v>229</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11334,7 +11341,7 @@
         <v>77</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>259</v>
+        <v>231</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>88</v>
@@ -11366,10 +11373,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11395,10 +11402,10 @@
         <v>104</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>263</v>
+        <v>235</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>264</v>
+        <v>475</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11449,7 +11456,7 @@
         <v>77</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>265</v>
+        <v>237</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -11481,13 +11488,13 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="D78" t="s" s="2">
         <v>77</v>
@@ -11512,7 +11519,7 @@
         <v>111</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="M78" t="s" s="2">
         <v>204</v>
@@ -11598,10 +11605,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11713,10 +11720,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11828,10 +11835,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11857,13 +11864,13 @@
         <v>133</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>255</v>
+        <v>227</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>256</v>
+        <v>228</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>257</v>
+        <v>229</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11871,7 +11878,7 @@
       </c>
       <c r="Q81" s="2"/>
       <c r="R81" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="S81" t="s" s="2">
         <v>77</v>
@@ -11913,7 +11920,7 @@
         <v>77</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>259</v>
+        <v>231</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>88</v>
@@ -11945,10 +11952,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11974,10 +11981,10 @@
         <v>104</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>263</v>
+        <v>235</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>264</v>
+        <v>475</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -12028,7 +12035,7 @@
         <v>77</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>265</v>
+        <v>237</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -12060,13 +12067,13 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C83" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="D83" t="s" s="2">
         <v>77</v>
@@ -12177,10 +12184,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12292,10 +12299,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12407,10 +12414,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12436,13 +12443,13 @@
         <v>133</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>255</v>
+        <v>227</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>256</v>
+        <v>228</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>257</v>
+        <v>229</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -12450,7 +12457,7 @@
       </c>
       <c r="Q86" s="2"/>
       <c r="R86" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="S86" t="s" s="2">
         <v>77</v>
@@ -12492,7 +12499,7 @@
         <v>77</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>259</v>
+        <v>231</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>88</v>
@@ -12524,10 +12531,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12553,10 +12560,10 @@
         <v>104</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>263</v>
+        <v>235</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>264</v>
+        <v>475</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12607,7 +12614,7 @@
         <v>77</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>265</v>
+        <v>237</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
@@ -12639,13 +12646,13 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="D88" t="s" s="2">
         <v>77</v>
@@ -12756,10 +12763,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12871,10 +12878,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12986,10 +12993,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13015,13 +13022,13 @@
         <v>133</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>255</v>
+        <v>227</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>256</v>
+        <v>228</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>257</v>
+        <v>229</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -13029,7 +13036,7 @@
       </c>
       <c r="Q91" s="2"/>
       <c r="R91" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="S91" t="s" s="2">
         <v>77</v>
@@ -13071,7 +13078,7 @@
         <v>77</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>259</v>
+        <v>231</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>88</v>
@@ -13103,10 +13110,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13129,13 +13136,13 @@
         <v>77</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>263</v>
+        <v>235</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>264</v>
+        <v>475</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -13186,7 +13193,7 @@
         <v>77</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>265</v>
+        <v>237</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -13218,10 +13225,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13247,13 +13254,13 @@
         <v>133</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>255</v>
+        <v>227</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>256</v>
+        <v>228</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>257</v>
+        <v>229</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13261,7 +13268,7 @@
       </c>
       <c r="Q93" s="2"/>
       <c r="R93" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="S93" t="s" s="2">
         <v>77</v>
@@ -13303,7 +13310,7 @@
         <v>77</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>259</v>
+        <v>231</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>88</v>
@@ -13335,10 +13342,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13361,13 +13368,13 @@
         <v>77</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>263</v>
+        <v>235</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>264</v>
+        <v>475</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -13418,7 +13425,7 @@
         <v>77</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>265</v>
+        <v>237</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -13450,13 +13457,13 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="D95" t="s" s="2">
         <v>77</v>
@@ -13478,13 +13485,13 @@
         <v>77</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -13567,13 +13574,13 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="D96" t="s" s="2">
         <v>77</v>
@@ -13595,13 +13602,13 @@
         <v>77</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -13684,13 +13691,13 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D97" t="s" s="2">
         <v>77</v>
@@ -13712,13 +13719,13 @@
         <v>77</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -13801,10 +13808,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13830,10 +13837,10 @@
         <v>178</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -13845,7 +13852,7 @@
         <v>77</v>
       </c>
       <c r="S98" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="T98" t="s" s="2">
         <v>77</v>
@@ -13863,10 +13870,10 @@
         <v>169</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>77</v>
@@ -13884,7 +13891,7 @@
         <v>77</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>78</v>
@@ -13893,7 +13900,7 @@
         <v>88</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AJ98" t="s" s="2">
         <v>101</v>
@@ -13902,13 +13909,13 @@
         <v>77</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>77</v>
@@ -13916,10 +13923,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13945,16 +13952,16 @@
         <v>104</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>77</v>
@@ -14003,7 +14010,7 @@
         <v>77</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>78</v>
@@ -14018,16 +14025,16 @@
         <v>101</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>77</v>
@@ -14035,10 +14042,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14064,16 +14071,16 @@
         <v>178</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>77</v>
@@ -14101,10 +14108,10 @@
         <v>169</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>77</v>
@@ -14122,7 +14129,7 @@
         <v>77</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
@@ -14140,13 +14147,13 @@
         <v>77</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>77</v>
@@ -14154,10 +14161,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14180,16 +14187,16 @@
         <v>89</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -14239,7 +14246,7 @@
         <v>77</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
@@ -14271,10 +14278,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14297,13 +14304,13 @@
         <v>89</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>262</v>
+        <v>234</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -14354,7 +14361,7 @@
         <v>77</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>78</v>
@@ -14375,10 +14382,10 @@
         <v>201</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>77</v>
@@ -14386,10 +14393,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14412,19 +14419,19 @@
         <v>77</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>77</v>
@@ -14473,7 +14480,7 @@
         <v>77</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>78</v>
@@ -14482,22 +14489,22 @@
         <v>79</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>77</v>
@@ -14505,10 +14512,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14531,17 +14538,17 @@
         <v>89</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>77</v>
@@ -14590,7 +14597,7 @@
         <v>77</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>78</v>
@@ -14608,10 +14615,10 @@
         <v>77</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="AN104" t="s" s="2">
         <v>108</v>
@@ -14622,10 +14629,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14737,10 +14744,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14854,10 +14861,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14883,13 +14890,13 @@
         <v>104</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -14939,7 +14946,7 @@
         <v>77</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>78</v>
@@ -14948,7 +14955,7 @@
         <v>88</v>
       </c>
       <c r="AI107" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="AJ107" t="s" s="2">
         <v>101</v>
@@ -14971,10 +14978,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15000,13 +15007,13 @@
         <v>133</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -15036,7 +15043,7 @@
       </c>
       <c r="Y108" s="2"/>
       <c r="Z108" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>77</v>
@@ -15054,7 +15061,7 @@
         <v>77</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>78</v>
@@ -15086,10 +15093,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15112,16 +15119,16 @@
         <v>89</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -15171,7 +15178,7 @@
         <v>77</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>78</v>
@@ -15192,7 +15199,7 @@
         <v>77</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>77</v>
@@ -15203,10 +15210,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15232,13 +15239,13 @@
         <v>104</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -15288,7 +15295,7 @@
         <v>77</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>78</v>
@@ -15320,10 +15327,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15346,19 +15353,19 @@
         <v>77</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>77</v>
@@ -15407,7 +15414,7 @@
         <v>77</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>78</v>
@@ -15428,7 +15435,7 @@
         <v>77</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="AN111" t="s" s="2">
         <v>77</v>
@@ -15439,10 +15446,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15554,10 +15561,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15671,14 +15678,14 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
@@ -15700,16 +15707,16 @@
         <v>111</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="N114" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>77</v>
@@ -15758,7 +15765,7 @@
         <v>77</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>78</v>
@@ -15790,10 +15797,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15816,17 +15823,17 @@
         <v>77</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>77</v>
@@ -15854,10 +15861,10 @@
         <v>154</v>
       </c>
       <c r="Y115" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="Z115" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="AA115" t="s" s="2">
         <v>77</v>
@@ -15875,7 +15882,7 @@
         <v>77</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>78</v>
@@ -15896,7 +15903,7 @@
         <v>77</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="AN115" t="s" s="2">
         <v>77</v>
@@ -15907,10 +15914,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15933,17 +15940,17 @@
         <v>77</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>77</v>
@@ -15992,7 +15999,7 @@
         <v>77</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>78</v>
@@ -16010,10 +16017,10 @@
         <v>77</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="AN116" t="s" s="2">
         <v>77</v>
@@ -16024,10 +16031,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16050,17 +16057,17 @@
         <v>77</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>77</v>
@@ -16109,7 +16116,7 @@
         <v>77</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>78</v>
@@ -16127,10 +16134,10 @@
         <v>77</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="AN117" t="s" s="2">
         <v>77</v>
@@ -16141,10 +16148,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16167,17 +16174,17 @@
         <v>77</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" t="s" s="2">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>77</v>
@@ -16226,7 +16233,7 @@
         <v>77</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>78</v>
@@ -16244,10 +16251,10 @@
         <v>77</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="AN118" t="s" s="2">
         <v>77</v>
@@ -16258,10 +16265,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16284,17 +16291,17 @@
         <v>77</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" t="s" s="2">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>77</v>
@@ -16343,7 +16350,7 @@
         <v>77</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>78</v>
